--- a/Plantilla Prueba_Guia .xlsx
+++ b/Plantilla Prueba_Guia .xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Tercer Semestre\Proyecto Integrador\Proyecto que integra\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\Programming\Java\Projects\Proyecto-Hospital\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21AFFEF4-4821-48E2-ADDD-C5EFE158C03F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{65C1E9DB-3B27-48A1-A7B7-4871A387322A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Horarios_Importar" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="51">
   <si>
     <t>fecha</t>
   </si>
@@ -175,9 +175,6 @@
   </si>
   <si>
     <t>UCI</t>
-  </si>
-  <si>
-    <t>Salud Mental</t>
   </si>
 </sst>
 </file>
@@ -297,7 +294,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -320,7 +317,6 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -332,12 +328,7 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="20" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -641,17 +632,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F10"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="5" width="13" customWidth="1"/>
     <col min="6" max="6" width="18" customWidth="1"/>
-    <col min="7" max="7" width="7.109375" customWidth="1"/>
+    <col min="7" max="7" width="7.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -671,88 +662,88 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>51</v>
+        <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="14">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="E2" s="14">
-        <v>0.58333333333333337</v>
+      <c r="D2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>12</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>51</v>
+        <v>13</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="15">
-        <v>0.58333333333333337</v>
-      </c>
-      <c r="E3" s="15">
-        <v>0.83333333333333337</v>
+      <c r="D3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>51</v>
+        <v>16</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="14">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="E4" s="14">
-        <v>0.58333333333333337</v>
+      <c r="D4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>17</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>51</v>
+        <v>7</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="15">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="E5" s="15">
-        <v>0.33333333333333331</v>
+      <c r="D5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>9</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="F10" s="8"/>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F10" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -763,7 +754,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="2" width="42" customWidth="1"/>
@@ -772,16 +763,16 @@
     <col min="5" max="5" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="11" t="s">
+    <row r="1" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-    </row>
-    <row r="2" spans="1:5" ht="27" x14ac:dyDescent="0.3">
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+    </row>
+    <row r="2" spans="1:5" ht="26.5" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
         <v>19</v>
       </c>
@@ -798,7 +789,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
         <v>0</v>
       </c>
@@ -815,7 +806,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="6" t="s">
         <v>1</v>
       </c>
@@ -832,7 +823,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="5" t="s">
         <v>2</v>
       </c>
@@ -849,7 +840,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="6" t="s">
         <v>3</v>
       </c>
@@ -866,7 +857,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="5" t="s">
         <v>4</v>
       </c>
@@ -883,7 +874,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="6" t="s">
         <v>5</v>
       </c>
@@ -900,41 +891,41 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="9" t="s">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A10" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="10"/>
-      <c r="C10" s="10"/>
-      <c r="D10" s="10"/>
-      <c r="E10" s="10"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="9" t="s">
+      <c r="B10" s="9"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A11" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="B11" s="10"/>
-      <c r="C11" s="10"/>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="9" t="s">
+      <c r="B11" s="9"/>
+      <c r="C11" s="9"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="9"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A12" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="10"/>
-      <c r="C12" s="10"/>
-      <c r="D12" s="10"/>
-      <c r="E12" s="10"/>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="12" t="s">
+      <c r="B12" s="9"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="9"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A13" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="B13" s="10"/>
-      <c r="C13" s="10"/>
-      <c r="D13" s="10"/>
-      <c r="E13" s="10"/>
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -951,7 +942,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:F7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -960,17 +951,17 @@
     <col min="6" max="6" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="s">
         <v>0</v>
       </c>
@@ -990,7 +981,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>44</v>
       </c>
@@ -1010,7 +1001,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>45</v>
       </c>
@@ -1030,7 +1021,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>46</v>
       </c>
@@ -1050,7 +1041,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
         <v>47</v>
       </c>
@@ -1070,7 +1061,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>49</v>
       </c>
